--- a/docs/assets/Timeline-Worksheet-2026.xlsx
+++ b/docs/assets/Timeline-Worksheet-2026.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernesto/github/MHACapstone/docs/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352E1617-AE36-3C4E-8EB3-1FE9AA013775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33FD8C7-CC20-B64B-991C-3F2AA033DC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="680" windowWidth="25380" windowHeight="27980" xr2:uid="{23EC970F-DE6B-9F48-9BEF-E3F42AA93A5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Prepare</t>
   </si>
@@ -73,15 +72,6 @@
   </si>
   <si>
     <t>To learn the methods and collect preliminary data</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>Presentation Day</t>
-  </si>
-  <si>
-    <t>Capstone Proposal</t>
   </si>
   <si>
     <t>Enter Your Name</t>
@@ -758,16 +748,16 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1197,49 +1187,49 @@
     <row r="3" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:4" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="48"/>
       <c r="D4" s="42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="48"/>
       <c r="D5" s="42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="49"/>
       <c r="D6" s="42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="51"/>
+      <c r="C8" s="54"/>
     </row>
     <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="50" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>26</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>7</v>
@@ -1255,19 +1245,19 @@
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" s="32">
         <v>45896</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="45">
         <v>45896</v>
@@ -1294,36 +1284,36 @@
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B15" s="30">
         <v>45952</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="18" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B16" s="30">
         <v>45980</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B17" s="30">
         <v>46003</v>
@@ -1353,26 +1343,26 @@
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B21" s="31">
         <v>45685</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1384,19 +1374,19 @@
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1404,18 +1394,18 @@
         <v>6</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="33" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="53">
+        <v>39</v>
+      </c>
+      <c r="B25" s="52">
         <v>45785</v>
       </c>
       <c r="C25" s="35"/>
@@ -1425,7 +1415,7 @@
       <c r="A26" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="54">
+      <c r="B26" s="53">
         <v>45785</v>
       </c>
       <c r="C26" s="16"/>
@@ -1452,96 +1442,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B549AB-D990-9647-B689-27426ADEB2AB}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3">
-        <v>45809</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="3">
-        <v>45915</v>
-      </c>
-      <c r="C2">
-        <f>_xlfn.DAYS(B2,B1)</f>
-        <v>106</v>
-      </c>
-      <c r="D2">
-        <f>C2/C4</f>
-        <v>0.32817337461300311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46011</v>
-      </c>
-      <c r="C3">
-        <f>_xlfn.DAYS(B3,B1)</f>
-        <v>202</v>
-      </c>
-      <c r="D3">
-        <f>C3/C4</f>
-        <v>0.62538699690402477</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46132</v>
-      </c>
-      <c r="C4">
-        <f>_xlfn.DAYS(B4,B1)</f>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46002</v>
-      </c>
-      <c r="C7">
-        <f>_xlfn.DAYS(B7,B6)</f>
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3">
-        <f>B6+(C7*D3)</f>
-        <v>45873.133126934983</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>